--- a/RESULTS_CONSOLIDATED.xlsx
+++ b/RESULTS_CONSOLIDATED.xlsx
@@ -531,12 +531,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="54" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -979,12 +979,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4. Base ensemble V2 (canonical)</t>
+          <t>6. Fusion analysis (V2 branches)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Base ensemble (alpha=0.6, no temperature)</t>
+          <t>M0 base ensemble (a=0.6)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1021,20 +1021,24 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>base essemble model experiment #1 (BERT + CNN &amp; NLP + GRU)/Result/Version 2 results/Base_Ensemble_Results.xlsx</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>improvement/Chapter4_Final_Tables.xlsx</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>CV macro-F1=0.5658</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6. Fusion analysis (V2 branches)</t>
+          <t>4. Base ensemble V2 (canonical)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M0 base ensemble (a=0.6)</t>
+          <t>Base ensemble (alpha=0.6, no temperature)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1071,14 +1075,10 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>improvement/Chapter4_Final_Tables.xlsx</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>CV macro-F1=0.5658</t>
-        </is>
-      </c>
+          <t>base essemble model experiment #1 (BERT + CNN &amp; NLP + GRU)/Result/Version 2 results/Base_Ensemble_Results.xlsx</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1349,54 +1349,486 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>0. Baseline (canonical)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Keras Word Tokenizer + LSTM</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Keras Word Tokenizer + LSTM</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>none (single model)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>60/20/10/10 canonical</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>984</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.5996</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.5896</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.5989</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Baseline experiment/canonical rerun/results/Baseline_Canonical_Results.xlsx</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>epoch 3 selected on val; class-weighted loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0. Baseline (canonical)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BERT Tokenizer + GRU</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BERT Tokenizer + GRU</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>none (single model)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>60/20/10/10 canonical</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>984</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.5823</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.5737</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.5839</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Baseline experiment/canonical rerun/results/Baseline_Canonical_Results.xlsx</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>epoch 4 selected on val; class-weighted loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0. Baseline (canonical)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Keras Word Tokenizer + GRU</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Keras Word Tokenizer + GRU</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>none (single model)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>60/20/10/10 canonical</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>984</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.5843</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.5721000000000001</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.5825</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Baseline experiment/canonical rerun/results/Baseline_Canonical_Results.xlsx</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>epoch 8 selected on val; class-weighted loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0. Baseline (canonical)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BERT Tokenizer + CNN</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BERT Tokenizer + CNN</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>none (single model)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>60/20/10/10 canonical</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>984</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.5854</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.5702</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.5817</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Baseline experiment/canonical rerun/results/Baseline_Canonical_Results.xlsx</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>epoch 6 selected on val; class-weighted loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0. Baseline (canonical)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Keras Word Tokenizer + CNN</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Keras Word Tokenizer + CNN</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>none (single model)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>60/20/10/10 canonical</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>984</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.5925</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.5696</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.5853</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Baseline experiment/canonical rerun/results/Baseline_Canonical_Results.xlsx</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>epoch 9 selected on val; class-weighted loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0. Baseline (canonical)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BERT Tokenizer + LSTM</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BERT Tokenizer + LSTM</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>none (single model)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>60/20/10/10 canonical</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>984</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.5711000000000001</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.5619</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Baseline experiment/canonical rerun/results/Baseline_Canonical_Results.xlsx</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>epoch 5 selected on val; class-weighted loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>6. Fusion analysis (V2 branches)</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>GRU branch alone</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>GRU+Keras + CNN+BERT</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>V2 (epoch Version 2: gru_best.pt / cnn_bert_best.pt)</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>60/20/10/10 canonical</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>984</v>
-      </c>
-      <c r="H16" t="n">
+      <c r="G22" t="n">
+        <v>984</v>
+      </c>
+      <c r="H22" t="n">
         <v>0.5732</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I22" t="n">
         <v>0.5459000000000001</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J22" t="n">
         <v>0.5627</v>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>improvement/Chapter4_Final_Tables.xlsx</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>not CV-selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0. Baseline (canonical)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Keras Word Tokenizer + RNN</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Keras Word Tokenizer + RNN</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>none (single model)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>60/20/10/10 canonical</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>984</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.5254</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.5167</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.5261</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Baseline experiment/canonical rerun/results/Baseline_Canonical_Results.xlsx</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>epoch 7 selected on val; class-weighted loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>0. Baseline (canonical)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>BERT Tokenizer + RNN</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BERT Tokenizer + RNN</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>none (single model)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>60/20/10/10 canonical</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>984</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.4421</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.4385</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.4381</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Baseline experiment/canonical rerun/results/Baseline_Canonical_Results.xlsx</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>epoch 8 selected on val; class-weighted loss</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1843,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="54" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
@@ -1493,401 +1925,449 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1. Baseline (single model)</t>
+          <t>0. Baseline (canonical)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NLP + CNN</t>
+          <t>Keras Word Tokenizer + LSTM</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NLP + CNN</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>Keras Word Tokenizer + LSTM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>none (single model)</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>80/20 own split</t>
+          <t>60/20/10/10 canonical</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>No - own split</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1967</v>
+        <v>984</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5486</v>
+        <v>0.5996</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5421</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
+        <v>0.5896</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.5989</v>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Mubin Master Finalize experiment.xlsx</t>
+          <t>Baseline experiment/canonical rerun/results/Baseline_Canonical_Results.xlsx</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Own train_test_split; test set not comparable to canonical 984-row test set</t>
+          <t>epoch 3 selected on val; class-weighted loss</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1. Baseline (single model)</t>
+          <t>0. Baseline (canonical)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NLP + GRU</t>
+          <t>BERT Tokenizer + GRU</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NLP + GRU</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>BERT Tokenizer + GRU</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>none (single model)</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>80/20 own split</t>
+          <t>60/20/10/10 canonical</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>No - own split</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1967</v>
+        <v>984</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5796</v>
+        <v>0.5823</v>
       </c>
       <c r="I3" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
+        <v>0.5737</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5839</v>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Mubin Master Finalize experiment.xlsx</t>
+          <t>Baseline experiment/canonical rerun/results/Baseline_Canonical_Results.xlsx</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Own train_test_split; test set not comparable to canonical 984-row test set</t>
+          <t>epoch 4 selected on val; class-weighted loss</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1. Baseline (single model)</t>
+          <t>0. Baseline (canonical)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NLP + LSTM</t>
+          <t>Keras Word Tokenizer + GRU</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NLP + LSTM</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Keras Word Tokenizer + GRU</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>none (single model)</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>80/20 own split</t>
+          <t>60/20/10/10 canonical</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>No - own split</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1967</v>
+        <v>984</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5506</v>
+        <v>0.5843</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5471</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
+        <v>0.5721000000000001</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.5825</v>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Mubin Master Finalize experiment.xlsx</t>
+          <t>Baseline experiment/canonical rerun/results/Baseline_Canonical_Results.xlsx</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Own train_test_split; test set not comparable to canonical 984-row test set</t>
+          <t>epoch 8 selected on val; class-weighted loss</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1. Baseline (single model)</t>
+          <t>0. Baseline (canonical)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NLP + RNN</t>
+          <t>BERT Tokenizer + CNN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NLP + RNN</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>BERT Tokenizer + CNN</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>none (single model)</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>80/20 own split</t>
+          <t>60/20/10/10 canonical</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>No - own split</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1967</v>
+        <v>984</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4926</v>
+        <v>0.5854</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4886</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
+        <v>0.5702</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5817</v>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Mubin Master Finalize experiment.xlsx</t>
+          <t>Baseline experiment/canonical rerun/results/Baseline_Canonical_Results.xlsx</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Own train_test_split; test set not comparable to canonical 984-row test set</t>
+          <t>epoch 6 selected on val; class-weighted loss</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1. Baseline (single model)</t>
+          <t>0. Baseline (canonical)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BERT + CNN</t>
+          <t>Keras Word Tokenizer + CNN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BERT + CNN</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Keras Word Tokenizer + CNN</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>none (single model)</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>80/20 own split</t>
+          <t>60/20/10/10 canonical</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>No - own split</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1967</v>
+        <v>984</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5948</v>
+        <v>0.5925</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5708</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
+        <v>0.5696</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5853</v>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Mubin Master Finalize experiment.xlsx</t>
+          <t>Baseline experiment/canonical rerun/results/Baseline_Canonical_Results.xlsx</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Own train_test_split; test set not comparable to canonical 984-row test set</t>
+          <t>epoch 9 selected on val; class-weighted loss</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1. Baseline (single model)</t>
+          <t>0. Baseline (canonical)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BERT + GRU</t>
+          <t>BERT Tokenizer + LSTM</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BERT + GRU</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>BERT Tokenizer + LSTM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>none (single model)</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>80/20 own split</t>
+          <t>60/20/10/10 canonical</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>No - own split</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1967</v>
+        <v>984</v>
       </c>
       <c r="H7" t="n">
-        <v>0.544</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5276</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
+        <v>0.5619</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.571</v>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Mubin Master Finalize experiment.xlsx</t>
+          <t>Baseline experiment/canonical rerun/results/Baseline_Canonical_Results.xlsx</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Own train_test_split; test set not comparable to canonical 984-row test set</t>
+          <t>epoch 5 selected on val; class-weighted loss</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1. Baseline (single model)</t>
+          <t>0. Baseline (canonical)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BERT + LSTM</t>
+          <t>Keras Word Tokenizer + RNN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BERT + LSTM</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Keras Word Tokenizer + RNN</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>none (single model)</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>80/20 own split</t>
+          <t>60/20/10/10 canonical</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>No - own split</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1967</v>
+        <v>984</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5653</v>
+        <v>0.5254</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5503</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
+        <v>0.5167</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.5261</v>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Mubin Master Finalize experiment.xlsx</t>
+          <t>Baseline experiment/canonical rerun/results/Baseline_Canonical_Results.xlsx</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Own train_test_split; test set not comparable to canonical 984-row test set</t>
+          <t>epoch 7 selected on val; class-weighted loss</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1. Baseline (single model)</t>
+          <t>0. Baseline (canonical)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BERT + RNN</t>
+          <t>BERT Tokenizer + RNN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BERT + RNN</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>BERT Tokenizer + RNN</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>none (single model)</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>80/20 own split</t>
+          <t>60/20/10/10 canonical</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>No - own split</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1967</v>
+        <v>984</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.4421</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5155</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
+        <v>0.4385</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.4381</v>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Mubin Master Finalize experiment.xlsx</t>
+          <t>Baseline experiment/canonical rerun/results/Baseline_Canonical_Results.xlsx</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Own train_test_split; test set not comparable to canonical 984-row test set</t>
+          <t>epoch 8 selected on val; class-weighted loss</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2. Base ensemble V1 (legacy)</t>
+          <t>1. Baseline (single model, superseded)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ensemble model 1 NLP + GRU BERT + CNN 2-way split</t>
+          <t>NLP + CNN</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NLP+GRU / BERT+CNN or LSTM</t>
+          <t>NLP + CNN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1905,10 +2385,10 @@
         <v>1967</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6026</v>
+        <v>0.5486</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5924</v>
+        <v>0.5421</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
@@ -1916,22 +2396,26 @@
           <t>Mubin Master Finalize experiment.xlsx</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Own train_test_split; test set not comparable to canonical 984-row test set. Superseded by stage 0. Note the four 'BERT + X' rows are BERT TOKENIZER + X - there is no BERT encoder in the baseline scripts.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2. Base ensemble V1 (legacy)</t>
+          <t>1. Baseline (single model, superseded)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ensemble model 2 NLP + GRU BERT + LSTM 2-way split</t>
+          <t>NLP + GRU</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NLP+GRU / BERT+CNN or LSTM</t>
+          <t>NLP + GRU</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -1949,10 +2433,10 @@
         <v>1967</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5696</v>
+        <v>0.5796</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5609</v>
+        <v>0.569</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
@@ -1960,359 +2444,335 @@
           <t>Mubin Master Finalize experiment.xlsx</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Own train_test_split; test set not comparable to canonical 984-row test set. Superseded by stage 0. Note the four 'BERT + X' rows are BERT TOKENIZER + X - there is no BERT encoder in the baseline scripts.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3. Optimised V1 (legacy, LEAKY)</t>
+          <t>1. Baseline (single model, superseded)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3-way split, epoch 5</t>
+          <t>NLP + LSTM</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NLP+GRU + BERT+CNN</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>V1 era (epoch_10: gru_keras10.pt / cnn_bert10.pt)</t>
-        </is>
-      </c>
+          <t>NLP + LSTM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>60/30/10 own split</t>
+          <t>80/20 own split</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>NO - LEAKAGE</t>
+          <t>No - own split</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>984</v>
+        <v>1967</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8577</v>
+        <v>0.5506</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8559</v>
+        <v>0.5471</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>optimised essemble model experiment #1 fix/ablation study/ablation_study_3way_vs_4way_split_epoch5.xlsx</t>
+          <t>Mubin Master Finalize experiment.xlsx</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Branches trained on 85% split; ensemble re-split independently -&gt; test rows seen in training</t>
+          <t>Own train_test_split; test set not comparable to canonical 984-row test set. Superseded by stage 0. Note the four 'BERT + X' rows are BERT TOKENIZER + X - there is no BERT encoder in the baseline scripts.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3. Optimised V1 (legacy, LEAKY)</t>
+          <t>1. Baseline (single model, superseded)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3-way split, epoch 6</t>
+          <t>NLP + RNN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NLP+GRU + BERT+CNN</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>V1 era (epoch_10: gru_keras10.pt / cnn_bert10.pt)</t>
-        </is>
-      </c>
+          <t>NLP + RNN</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>60/30/10 own split</t>
+          <t>80/20 own split</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>NO - LEAKAGE</t>
+          <t>No - own split</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>984</v>
+        <v>1967</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8516</v>
+        <v>0.4926</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8506</v>
+        <v>0.4886</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>optimised essemble model experiment #1 fix/ablation study/ablation_study_3way_vs_4way_split_epoch6.xlsx</t>
+          <t>Mubin Master Finalize experiment.xlsx</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Branches trained on 85% split; ensemble re-split independently -&gt; test rows seen in training</t>
+          <t>Own train_test_split; test set not comparable to canonical 984-row test set. Superseded by stage 0. Note the four 'BERT + X' rows are BERT TOKENIZER + X - there is no BERT encoder in the baseline scripts.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3. Optimised V1 (legacy, LEAKY)</t>
+          <t>1. Baseline (single model, superseded)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3-way split, epoch 7</t>
+          <t>BERT + CNN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NLP+GRU + BERT+CNN</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>V1 era (epoch_10: gru_keras10.pt / cnn_bert10.pt)</t>
-        </is>
-      </c>
+          <t>BERT + CNN</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>60/30/10 own split</t>
+          <t>80/20 own split</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>NO - LEAKAGE</t>
+          <t>No - own split</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>984</v>
+        <v>1967</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8557</v>
+        <v>0.5948</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8526</v>
+        <v>0.5708</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>optimised essemble model experiment #1 fix/ablation study/ablation_study_3way_vs_4way_split_epoch7.xlsx</t>
+          <t>Mubin Master Finalize experiment.xlsx</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Branches trained on 85% split; ensemble re-split independently -&gt; test rows seen in training</t>
+          <t>Own train_test_split; test set not comparable to canonical 984-row test set. Superseded by stage 0. Note the four 'BERT + X' rows are BERT TOKENIZER + X - there is no BERT encoder in the baseline scripts.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3. Optimised V1 (legacy, LEAKY)</t>
+          <t>1. Baseline (single model, superseded)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3-way split, epoch 8</t>
+          <t>BERT + GRU</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NLP+GRU + BERT+CNN</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>V1 era (epoch_10: gru_keras10.pt / cnn_bert10.pt)</t>
-        </is>
-      </c>
+          <t>BERT + GRU</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>60/30/10 own split</t>
+          <t>80/20 own split</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>NO - LEAKAGE</t>
+          <t>No - own split</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>984</v>
+        <v>1967</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8618</v>
+        <v>0.544</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8606</v>
+        <v>0.5276</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>optimised essemble model experiment #1 fix/ablation study/ablation_study_3way_vs_4way_split_epoch8.xlsx</t>
+          <t>Mubin Master Finalize experiment.xlsx</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Branches trained on 85% split; ensemble re-split independently -&gt; test rows seen in training</t>
+          <t>Own train_test_split; test set not comparable to canonical 984-row test set. Superseded by stage 0. Note the four 'BERT + X' rows are BERT TOKENIZER + X - there is no BERT encoder in the baseline scripts.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3. Optimised V1 (legacy, LEAKY)</t>
+          <t>1. Baseline (single model, superseded)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3-way split, epoch 9</t>
+          <t>BERT + LSTM</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NLP+GRU + BERT+CNN</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>V1 era (epoch_10: gru_keras10.pt / cnn_bert10.pt)</t>
-        </is>
-      </c>
+          <t>BERT + LSTM</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>60/30/10 own split</t>
+          <t>80/20 own split</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>NO - LEAKAGE</t>
+          <t>No - own split</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>984</v>
+        <v>1967</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8506</v>
+        <v>0.5653</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8484</v>
+        <v>0.5503</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>optimised essemble model experiment #1 fix/ablation study/ablation_study_3way_vs_4way_split_epoch9.xlsx</t>
+          <t>Mubin Master Finalize experiment.xlsx</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Branches trained on 85% split; ensemble re-split independently -&gt; test rows seen in training</t>
+          <t>Own train_test_split; test set not comparable to canonical 984-row test set. Superseded by stage 0. Note the four 'BERT + X' rows are BERT TOKENIZER + X - there is no BERT encoder in the baseline scripts.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3. Optimised V1 (legacy, LEAKY)</t>
+          <t>1. Baseline (single model, superseded)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3-way split, epoch 10</t>
+          <t>BERT + RNN</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NLP+GRU + BERT+CNN</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>V1 era (epoch_10: gru_keras10.pt / cnn_bert10.pt)</t>
-        </is>
-      </c>
+          <t>BERT + RNN</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>60/30/10 own split</t>
+          <t>80/20 own split</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>NO - LEAKAGE</t>
+          <t>No - own split</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>984</v>
+        <v>1967</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8567</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8549</v>
+        <v>0.5155</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>optimised essemble model experiment #1 fix/ablation study/ablation_study_3way_vs_4way_split_epoch10.xlsx</t>
+          <t>Mubin Master Finalize experiment.xlsx</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Branches trained on 85% split; ensemble re-split independently -&gt; test rows seen in training</t>
+          <t>Own train_test_split; test set not comparable to canonical 984-row test set. Superseded by stage 0. Note the four 'BERT + X' rows are BERT TOKENIZER + X - there is no BERT encoder in the baseline scripts.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3. Optimised V1 (legacy, LEAKY)</t>
+          <t>2. Base ensemble V1 (legacy)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3-way (60-30-10), epoch 5</t>
+          <t>Ensemble model 1 NLP + GRU BERT + CNN 2-way split</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NLP+GRU + BERT+CNN</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>V1 era (epoch_10: gru_keras10.pt / cnn_bert10.pt)</t>
-        </is>
-      </c>
+          <t>NLP+GRU / BERT+CNN or LSTM</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3-way (60-30-10)</t>
+          <t>80/20 own split</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>NO - LEAKAGE</t>
+          <t>No - own split</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>984</v>
+        <v>1967</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8577</v>
+        <v>0.6026</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8559</v>
+        <v>0.5924</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
@@ -2320,51 +2780,43 @@
           <t>Mubin Master Finalize experiment.xlsx</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Inflated by leakage - superseded by canonical-split reruns</t>
-        </is>
-      </c>
+      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3. Optimised V1 (legacy, LEAKY)</t>
+          <t>2. Base ensemble V1 (legacy)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3-way (60-30-10), epoch 6</t>
+          <t>Ensemble model 2 NLP + GRU BERT + LSTM 2-way split</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NLP+GRU + BERT+CNN</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>V1 era (epoch_10: gru_keras10.pt / cnn_bert10.pt)</t>
-        </is>
-      </c>
+          <t>NLP+GRU / BERT+CNN or LSTM</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3-way (60-30-10)</t>
+          <t>80/20 own split</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>NO - LEAKAGE</t>
+          <t>No - own split</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>984</v>
+        <v>1967</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8516</v>
+        <v>0.5696</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8506</v>
+        <v>0.5609</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
@@ -2372,11 +2824,7 @@
           <t>Mubin Master Finalize experiment.xlsx</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Inflated by leakage - superseded by canonical-split reruns</t>
-        </is>
-      </c>
+      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2386,7 +2834,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3-way (60-30-10), epoch 7</t>
+          <t>3-way split, epoch 5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2401,7 +2849,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3-way (60-30-10)</t>
+          <t>60/30/10 own split</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2413,20 +2861,20 @@
         <v>984</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8557</v>
+        <v>0.8577</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8526</v>
+        <v>0.8559</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Mubin Master Finalize experiment.xlsx</t>
+          <t>optimised essemble model experiment #1 fix/ablation study/ablation_study_3way_vs_4way_split_epoch5.xlsx</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Inflated by leakage - superseded by canonical-split reruns</t>
+          <t>Branches trained on 85% split; ensemble re-split independently -&gt; test rows seen in training</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2886,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3-way (60-30-10), epoch 8</t>
+          <t>3-way split, epoch 6</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2453,7 +2901,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3-way (60-30-10)</t>
+          <t>60/30/10 own split</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2465,20 +2913,20 @@
         <v>984</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8618</v>
+        <v>0.8516</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8606</v>
+        <v>0.8506</v>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Mubin Master Finalize experiment.xlsx</t>
+          <t>optimised essemble model experiment #1 fix/ablation study/ablation_study_3way_vs_4way_split_epoch6.xlsx</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Inflated by leakage - superseded by canonical-split reruns</t>
+          <t>Branches trained on 85% split; ensemble re-split independently -&gt; test rows seen in training</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2938,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3-way (60-30-10), epoch 9</t>
+          <t>3-way split, epoch 7</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2505,7 +2953,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3-way (60-30-10)</t>
+          <t>60/30/10 own split</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2517,20 +2965,20 @@
         <v>984</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8506</v>
+        <v>0.8557</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8484</v>
+        <v>0.8526</v>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Mubin Master Finalize experiment.xlsx</t>
+          <t>optimised essemble model experiment #1 fix/ablation study/ablation_study_3way_vs_4way_split_epoch7.xlsx</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Inflated by leakage - superseded by canonical-split reruns</t>
+          <t>Branches trained on 85% split; ensemble re-split independently -&gt; test rows seen in training</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2990,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3-way (60-30-10), epoch 10</t>
+          <t>3-way split, epoch 8</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2557,7 +3005,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3-way (60-30-10)</t>
+          <t>60/30/10 own split</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2569,20 +3017,20 @@
         <v>984</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8567</v>
+        <v>0.8618</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8549</v>
+        <v>0.8606</v>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Mubin Master Finalize experiment.xlsx</t>
+          <t>optimised essemble model experiment #1 fix/ablation study/ablation_study_3way_vs_4way_split_epoch8.xlsx</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Inflated by leakage - superseded by canonical-split reruns</t>
+          <t>Branches trained on 85% split; ensemble re-split independently -&gt; test rows seen in training</t>
         </is>
       </c>
     </row>
@@ -2594,7 +3042,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4-way (60-20-10-10), epoch 5</t>
+          <t>3-way split, epoch 9</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2609,7 +3057,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>4-way (60-20-10-10)</t>
+          <t>60/30/10 own split</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2621,20 +3069,20 @@
         <v>984</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8669</v>
+        <v>0.8506</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8655</v>
+        <v>0.8484</v>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Mubin Master Finalize experiment.xlsx</t>
+          <t>optimised essemble model experiment #1 fix/ablation study/ablation_study_3way_vs_4way_split_epoch9.xlsx</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Inflated by leakage - superseded by canonical-split reruns</t>
+          <t>Branches trained on 85% split; ensemble re-split independently -&gt; test rows seen in training</t>
         </is>
       </c>
     </row>
@@ -2646,7 +3094,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4-way (60-20-10-10), epoch 6</t>
+          <t>3-way split, epoch 10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2661,7 +3109,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>4-way (60-20-10-10)</t>
+          <t>60/30/10 own split</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2673,20 +3121,20 @@
         <v>984</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8679</v>
+        <v>0.8567</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8668</v>
+        <v>0.8549</v>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Mubin Master Finalize experiment.xlsx</t>
+          <t>optimised essemble model experiment #1 fix/ablation study/ablation_study_3way_vs_4way_split_epoch10.xlsx</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Inflated by leakage - superseded by canonical-split reruns</t>
+          <t>Branches trained on 85% split; ensemble re-split independently -&gt; test rows seen in training</t>
         </is>
       </c>
     </row>
@@ -2698,7 +3146,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4-way (60-20-10-10), epoch 7</t>
+          <t>3-way (60-30-10), epoch 5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2713,7 +3161,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>4-way (60-20-10-10)</t>
+          <t>3-way (60-30-10)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2725,10 +3173,10 @@
         <v>984</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8669</v>
+        <v>0.8577</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8655</v>
+        <v>0.8559</v>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
@@ -2750,7 +3198,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4-way (60-20-10-10), epoch 8</t>
+          <t>3-way (60-30-10), epoch 6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2765,7 +3213,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>4-way (60-20-10-10)</t>
+          <t>3-way (60-30-10)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2777,10 +3225,10 @@
         <v>984</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8638</v>
+        <v>0.8516</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8621</v>
+        <v>0.8506</v>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
@@ -2802,7 +3250,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>4-way (60-20-10-10), epoch 9</t>
+          <t>3-way (60-30-10), epoch 7</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2817,7 +3265,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>4-way (60-20-10-10)</t>
+          <t>3-way (60-30-10)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2829,10 +3277,10 @@
         <v>984</v>
       </c>
       <c r="H28" t="n">
-        <v>0.8537</v>
+        <v>0.8557</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8534</v>
+        <v>0.8526</v>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
@@ -2854,7 +3302,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4-way (60-20-10-10), epoch 10</t>
+          <t>3-way (60-30-10), epoch 8</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2869,7 +3317,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>4-way (60-20-10-10)</t>
+          <t>3-way (60-30-10)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2881,10 +3329,10 @@
         <v>984</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8709</v>
+        <v>0.8618</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8704</v>
+        <v>0.8606</v>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
@@ -2901,440 +3349,428 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4. Base ensemble V2 (canonical)</t>
+          <t>3. Optimised V1 (legacy, LEAKY)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Base ensemble (alpha=0.6, no temperature)</t>
+          <t>3-way (60-30-10), epoch 9</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GRU+Keras + CNN+BERT</t>
+          <t>NLP+GRU + BERT+CNN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>V2 (epoch Version 2: gru_best.pt / cnn_bert_best.pt)</t>
+          <t>V1 era (epoch_10: gru_keras10.pt / cnn_bert10.pt)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>60/20/10/10 canonical</t>
+          <t>3-way (60-30-10)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NO - LEAKAGE</t>
         </is>
       </c>
       <c r="G30" t="n">
         <v>984</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6341</v>
+        <v>0.8506</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6218</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.6306</v>
-      </c>
+        <v>0.8484</v>
+      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>base essemble model experiment #1 (BERT + CNN &amp; NLP + GRU)/Result/Version 2 results/Base_Ensemble_Results.xlsx</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
+          <t>Mubin Master Finalize experiment.xlsx</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Inflated by leakage - superseded by canonical-split reruns</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5. Optimised V2 (canonical)</t>
+          <t>3. Optimised V1 (legacy, LEAKY)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Alpha grid search + temperature</t>
+          <t>3-way (60-30-10), epoch 10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GRU+Keras + CNN+BERT</t>
+          <t>NLP+GRU + BERT+CNN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>V2 (epoch Version 2: gru_best.pt / cnn_bert_best.pt)</t>
+          <t>V1 era (epoch_10: gru_keras10.pt / cnn_bert10.pt)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>60/20/10/10 canonical</t>
+          <t>3-way (60-30-10)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NO - LEAKAGE</t>
         </is>
       </c>
       <c r="G31" t="n">
         <v>984</v>
       </c>
       <c r="H31" t="n">
-        <v>0.625</v>
+        <v>0.8567</v>
       </c>
       <c r="I31" t="n">
-        <v>0.6142</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.6223</v>
-      </c>
+        <v>0.8549</v>
+      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>optimised essemble model experiment #1 fix/result 4 way V2/Optimized_Ensemble_Results.xlsx</t>
+          <t>Mubin Master Finalize experiment.xlsx</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>alpha=0.7000000000000001, T_cnn=1.37, T_gru=1.415</t>
+          <t>Inflated by leakage - superseded by canonical-split reruns</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6. Fusion analysis (V2 branches)</t>
+          <t>3. Optimised V1 (legacy, LEAKY)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GRU branch alone</t>
+          <t>4-way (60-20-10-10), epoch 5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GRU+Keras + CNN+BERT</t>
+          <t>NLP+GRU + BERT+CNN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>V2 (epoch Version 2: gru_best.pt / cnn_bert_best.pt)</t>
+          <t>V1 era (epoch_10: gru_keras10.pt / cnn_bert10.pt)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>60/20/10/10 canonical</t>
+          <t>4-way (60-20-10-10)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NO - LEAKAGE</t>
         </is>
       </c>
       <c r="G32" t="n">
         <v>984</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5732</v>
+        <v>0.8669</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5459000000000001</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0.5627</v>
-      </c>
+        <v>0.8655</v>
+      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>improvement/Chapter4_Final_Tables.xlsx</t>
+          <t>Mubin Master Finalize experiment.xlsx</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>not CV-selected</t>
+          <t>Inflated by leakage - superseded by canonical-split reruns</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6. Fusion analysis (V2 branches)</t>
+          <t>3. Optimised V1 (legacy, LEAKY)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CNN-BERT branch alone</t>
+          <t>4-way (60-20-10-10), epoch 6</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GRU+Keras + CNN+BERT</t>
+          <t>NLP+GRU + BERT+CNN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>V2 (epoch Version 2: gru_best.pt / cnn_bert_best.pt)</t>
+          <t>V1 era (epoch_10: gru_keras10.pt / cnn_bert10.pt)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>60/20/10/10 canonical</t>
+          <t>4-way (60-20-10-10)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NO - LEAKAGE</t>
         </is>
       </c>
       <c r="G33" t="n">
         <v>984</v>
       </c>
       <c r="H33" t="n">
-        <v>0.6138</v>
+        <v>0.8679</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6052999999999999</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0.6124000000000001</v>
-      </c>
+        <v>0.8668</v>
+      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>improvement/Chapter4_Final_Tables.xlsx</t>
+          <t>Mubin Master Finalize experiment.xlsx</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>not CV-selected</t>
+          <t>Inflated by leakage - superseded by canonical-split reruns</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6. Fusion analysis (V2 branches)</t>
+          <t>3. Optimised V1 (legacy, LEAKY)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>M0 base ensemble (a=0.6)</t>
+          <t>4-way (60-20-10-10), epoch 7</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GRU+Keras + CNN+BERT</t>
+          <t>NLP+GRU + BERT+CNN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>V2 (epoch Version 2: gru_best.pt / cnn_bert_best.pt)</t>
+          <t>V1 era (epoch_10: gru_keras10.pt / cnn_bert10.pt)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>60/20/10/10 canonical</t>
+          <t>4-way (60-20-10-10)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NO - LEAKAGE</t>
         </is>
       </c>
       <c r="G34" t="n">
         <v>984</v>
       </c>
       <c r="H34" t="n">
-        <v>0.6341</v>
+        <v>0.8669</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6218</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.6306</v>
-      </c>
+        <v>0.8655</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>improvement/Chapter4_Final_Tables.xlsx</t>
+          <t>Mubin Master Finalize experiment.xlsx</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CV macro-F1=0.5658</t>
+          <t>Inflated by leakage - superseded by canonical-split reruns</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6. Fusion analysis (V2 branches)</t>
+          <t>3. Optimised V1 (legacy, LEAKY)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Old optimized (a=0.7, T)</t>
+          <t>4-way (60-20-10-10), epoch 8</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GRU+Keras + CNN+BERT</t>
+          <t>NLP+GRU + BERT+CNN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>V2 (epoch Version 2: gru_best.pt / cnn_bert_best.pt)</t>
+          <t>V1 era (epoch_10: gru_keras10.pt / cnn_bert10.pt)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>60/20/10/10 canonical</t>
+          <t>4-way (60-20-10-10)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NO - LEAKAGE</t>
         </is>
       </c>
       <c r="G35" t="n">
         <v>984</v>
       </c>
       <c r="H35" t="n">
-        <v>0.626</v>
+        <v>0.8638</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6147</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0.6229</v>
-      </c>
+        <v>0.8621</v>
+      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>improvement/Chapter4_Final_Tables.xlsx</t>
+          <t>Mubin Master Finalize experiment.xlsx</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>not CV-selected</t>
+          <t>Inflated by leakage - superseded by canonical-split reruns</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6. Fusion analysis (V2 branches)</t>
+          <t>3. Optimised V1 (legacy, LEAKY)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>M1 fitted scalar alpha</t>
+          <t>4-way (60-20-10-10), epoch 9</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GRU+Keras + CNN+BERT</t>
+          <t>NLP+GRU + BERT+CNN</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>V2 (epoch Version 2: gru_best.pt / cnn_bert_best.pt)</t>
+          <t>V1 era (epoch_10: gru_keras10.pt / cnn_bert10.pt)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>60/20/10/10 canonical</t>
+          <t>4-way (60-20-10-10)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NO - LEAKAGE</t>
         </is>
       </c>
       <c r="G36" t="n">
         <v>984</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6291</v>
+        <v>0.8537</v>
       </c>
       <c r="I36" t="n">
-        <v>0.6185</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.6264</v>
-      </c>
+        <v>0.8534</v>
+      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>improvement/Chapter4_Final_Tables.xlsx</t>
+          <t>Mubin Master Finalize experiment.xlsx</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CV macro-F1=0.5552</t>
+          <t>Inflated by leakage - superseded by canonical-split reruns</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6. Fusion analysis (V2 branches)</t>
+          <t>3. Optimised V1 (legacy, LEAKY)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>M2 alpha + class bias</t>
+          <t>4-way (60-20-10-10), epoch 10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GRU+Keras + CNN+BERT</t>
+          <t>NLP+GRU + BERT+CNN</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>V2 (epoch Version 2: gru_best.pt / cnn_bert_best.pt)</t>
+          <t>V1 era (epoch_10: gru_keras10.pt / cnn_bert10.pt)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>60/20/10/10 canonical</t>
+          <t>4-way (60-20-10-10)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NO - LEAKAGE</t>
         </is>
       </c>
       <c r="G37" t="n">
         <v>984</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6413</v>
+        <v>0.8709</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6308</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0.6398</v>
-      </c>
+        <v>0.8704</v>
+      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>improvement/Chapter4_Final_Tables.xlsx</t>
+          <t>Mubin Master Finalize experiment.xlsx</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CV macro-F1=0.5903</t>
+          <t>Inflated by leakage - superseded by canonical-split reruns</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6. Fusion analysis (V2 branches)</t>
+          <t>4. Base ensemble V2 (canonical)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>M3 per-class weights + bias</t>
+          <t>Base ensemble (alpha=0.6, no temperature)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3361,34 +3797,30 @@
         <v>984</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6392</v>
+        <v>0.6341</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6283</v>
+        <v>0.6218</v>
       </c>
       <c r="J38" t="n">
-        <v>0.6377</v>
+        <v>0.6306</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>improvement/Chapter4_Final_Tables.xlsx</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>CV macro-F1=0.5887</t>
-        </is>
-      </c>
+          <t>base essemble model experiment #1 (BERT + CNN &amp; NLP + GRU)/Result/Version 2 results/Base_Ensemble_Results.xlsx</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6. Fusion analysis (V2 branches)</t>
+          <t>5. Optimised V2 (canonical)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>S1 stacker (cal only)</t>
+          <t>Alpha grid search + temperature</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3415,22 +3847,22 @@
         <v>984</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6443</v>
+        <v>0.625</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6387</v>
+        <v>0.6142</v>
       </c>
       <c r="J39" t="n">
-        <v>0.6448</v>
+        <v>0.6223</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>improvement/Chapter4_Final_Tables.xlsx</t>
+          <t>optimised essemble model experiment #1 fix/result 4 way V2/Optimized_Ensemble_Results.xlsx</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CV macro-F1=0.6001725041531768</t>
+          <t>alpha=0.7000000000000001, T_cnn=1.37, T_gru=1.415</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3874,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>S2 stacker (val+cal)</t>
+          <t>GRU branch alone</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3469,13 +3901,13 @@
         <v>984</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6494</v>
+        <v>0.5732</v>
       </c>
       <c r="I40" t="n">
-        <v>0.644</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>0.6499</v>
+        <v>0.5627</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3491,12 +3923,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>7. Tuned V3 (canonical)</t>
+          <t>6. Fusion analysis (V2 branches)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GRU + Keras (single branch)</t>
+          <t>CNN-BERT branch alone</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3506,7 +3938,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>V3 tuned (tuned GRU|CNN BERT model/V3)</t>
+          <t>V2 (epoch Version 2: gru_best.pt / cnn_bert_best.pt)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3523,30 +3955,34 @@
         <v>984</v>
       </c>
       <c r="H41" t="n">
-        <v>0.624</v>
+        <v>0.6138</v>
       </c>
       <c r="I41" t="n">
-        <v>0.6194</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>0.6254</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>base essemble model experiment #1 (BERT + CNN &amp; NLP + GRU)/Result/Version 3 tuned results/Tuned_Ensemble_Results.xlsx</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
+          <t>improvement/Chapter4_Final_Tables.xlsx</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>not CV-selected</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>7. Tuned V3 (canonical)</t>
+          <t>6. Fusion analysis (V2 branches)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CNN + BERT (single branch)</t>
+          <t>M0 base ensemble (a=0.6)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3556,7 +3992,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>V3 tuned (tuned GRU|CNN BERT model/V3)</t>
+          <t>V2 (epoch Version 2: gru_best.pt / cnn_bert_best.pt)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3573,30 +4009,34 @@
         <v>984</v>
       </c>
       <c r="H42" t="n">
-        <v>0.6382</v>
+        <v>0.6341</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6309</v>
+        <v>0.6218</v>
       </c>
       <c r="J42" t="n">
-        <v>0.6375999999999999</v>
+        <v>0.6306</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>base essemble model experiment #1 (BERT + CNN &amp; NLP + GRU)/Result/Version 3 tuned results/Tuned_Ensemble_Results.xlsx</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
+          <t>improvement/Chapter4_Final_Tables.xlsx</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>CV macro-F1=0.5658</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>7. Tuned V3 (canonical)</t>
+          <t>6. Fusion analysis (V2 branches)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Base ensemble (a=0.6, b=0.4, T=1)</t>
+          <t>Old optimized (a=0.7, T)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3606,7 +4046,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>V3 tuned (tuned GRU|CNN BERT model/V3)</t>
+          <t>V2 (epoch Version 2: gru_best.pt / cnn_bert_best.pt)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3623,70 +4063,494 @@
         <v>984</v>
       </c>
       <c r="H43" t="n">
-        <v>0.6646</v>
+        <v>0.626</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6586</v>
+        <v>0.6147</v>
       </c>
       <c r="J43" t="n">
-        <v>0.6651</v>
+        <v>0.6229</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>base essemble model experiment #1 (BERT + CNN &amp; NLP + GRU)/Result/Version 3 tuned results/Tuned_Ensemble_Results.xlsx</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
+          <t>improvement/Chapter4_Final_Tables.xlsx</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>not CV-selected</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>6. Fusion analysis (V2 branches)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>M1 fitted scalar alpha</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>GRU+Keras + CNN+BERT</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>V2 (epoch Version 2: gru_best.pt / cnn_bert_best.pt)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>60/20/10/10 canonical</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>984</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.6291</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.6185</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.6264</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>improvement/Chapter4_Final_Tables.xlsx</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>CV macro-F1=0.5552</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>6. Fusion analysis (V2 branches)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>M2 alpha + class bias</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>GRU+Keras + CNN+BERT</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>V2 (epoch Version 2: gru_best.pt / cnn_bert_best.pt)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>60/20/10/10 canonical</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>984</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.6413</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.6308</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.6398</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>improvement/Chapter4_Final_Tables.xlsx</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>CV macro-F1=0.5903</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>6. Fusion analysis (V2 branches)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>M3 per-class weights + bias</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>GRU+Keras + CNN+BERT</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>V2 (epoch Version 2: gru_best.pt / cnn_bert_best.pt)</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>60/20/10/10 canonical</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>984</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.6392</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.6283</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.6377</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>improvement/Chapter4_Final_Tables.xlsx</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>CV macro-F1=0.5887</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>6. Fusion analysis (V2 branches)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>S1 stacker (cal only)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>GRU+Keras + CNN+BERT</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>V2 (epoch Version 2: gru_best.pt / cnn_bert_best.pt)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>60/20/10/10 canonical</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>984</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.6443</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.6387</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.6448</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>improvement/Chapter4_Final_Tables.xlsx</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>CV macro-F1=0.6001725041531768</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>6. Fusion analysis (V2 branches)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>S2 stacker (val+cal)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>GRU+Keras + CNN+BERT</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>V2 (epoch Version 2: gru_best.pt / cnn_bert_best.pt)</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>60/20/10/10 canonical</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>984</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.6494</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.6499</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>improvement/Chapter4_Final_Tables.xlsx</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>not CV-selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>7. Tuned V3 (canonical)</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>GRU + Keras (single branch)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>GRU+Keras + CNN+BERT</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>V3 tuned (tuned GRU|CNN BERT model/V3)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>60/20/10/10 canonical</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>984</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.6194</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.6254</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>base essemble model experiment #1 (BERT + CNN &amp; NLP + GRU)/Result/Version 3 tuned results/Tuned_Ensemble_Results.xlsx</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>7. Tuned V3 (canonical)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CNN + BERT (single branch)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>GRU+Keras + CNN+BERT</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>V3 tuned (tuned GRU|CNN BERT model/V3)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>60/20/10/10 canonical</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>984</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.6382</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.6309</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.6375999999999999</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>base essemble model experiment #1 (BERT + CNN &amp; NLP + GRU)/Result/Version 3 tuned results/Tuned_Ensemble_Results.xlsx</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>7. Tuned V3 (canonical)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Base ensemble (a=0.6, b=0.4, T=1)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>GRU+Keras + CNN+BERT</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>V3 tuned (tuned GRU|CNN BERT model/V3)</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>60/20/10/10 canonical</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>984</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.6646</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.6586</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.6651</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>base essemble model experiment #1 (BERT + CNN &amp; NLP + GRU)/Result/Version 3 tuned results/Tuned_Ensemble_Results.xlsx</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>7. Tuned V3 (canonical)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
         <is>
           <t>Tuned ensemble (a=0.55, T_cnn=0.75, T_gru=1.25)</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>GRU+Keras + CNN+BERT</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>V3 tuned (tuned GRU|CNN BERT model/V3)</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>60/20/10/10 canonical</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>984</v>
-      </c>
-      <c r="H44" t="n">
+      <c r="G52" t="n">
+        <v>984</v>
+      </c>
+      <c r="H52" t="n">
         <v>0.6728</v>
       </c>
-      <c r="I44" t="n">
+      <c r="I52" t="n">
         <v>0.6664</v>
       </c>
-      <c r="J44" t="n">
+      <c r="J52" t="n">
         <v>0.6727</v>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>base essemble model experiment #1 (BERT + CNN &amp; NLP + GRU)/Result/Version 3 tuned results/Tuned_Ensemble_Results.xlsx</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3699,10 +4563,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
@@ -4006,6 +4870,93 @@
       <c r="G10" t="inlineStr">
         <is>
           <t>improvement/Chapter4_Final_Tables.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Keras Word Tokenizer + LSTM (best canonical baseline)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.6095238095238096</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.6368159203980099</v>
+      </c>
+      <c r="F11" t="n">
+        <v>420</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Baseline experiment/canonical rerun/results/Baseline_Canonical_Results.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Keras Word Tokenizer + LSTM (best canonical baseline)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.5358649789029536</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.4941634241245136</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.5141700404858299</v>
+      </c>
+      <c r="F12" t="n">
+        <v>257</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Baseline experiment/canonical rerun/results/Baseline_Canonical_Results.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Keras Word Tokenizer + LSTM (best canonical baseline)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.5702479338842975</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.6742671009771987</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.6179104477611941</v>
+      </c>
+      <c r="F13" t="n">
+        <v>307</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Baseline experiment/canonical rerun/results/Baseline_Canonical_Results.xlsx</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4974,7 @@
   <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="51" customWidth="1" min="4" max="4"/>
@@ -4102,7 +5053,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1. Baseline (single model)</t>
+          <t>1. Baseline (single model, superseded)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4143,14 +5094,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Own train_test_split; test set not comparable to canonical 984-row test set</t>
+          <t>Own train_test_split; test set not comparable to canonical 984-row test set. Superseded by stage 0. Note the four 'BERT + X' rows are BERT TOKENIZER + X - there is no BERT encoder in the baseline scripts.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1. Baseline (single model)</t>
+          <t>1. Baseline (single model, superseded)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4191,14 +5142,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Own train_test_split; test set not comparable to canonical 984-row test set</t>
+          <t>Own train_test_split; test set not comparable to canonical 984-row test set. Superseded by stage 0. Note the four 'BERT + X' rows are BERT TOKENIZER + X - there is no BERT encoder in the baseline scripts.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1. Baseline (single model)</t>
+          <t>1. Baseline (single model, superseded)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4239,14 +5190,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Own train_test_split; test set not comparable to canonical 984-row test set</t>
+          <t>Own train_test_split; test set not comparable to canonical 984-row test set. Superseded by stage 0. Note the four 'BERT + X' rows are BERT TOKENIZER + X - there is no BERT encoder in the baseline scripts.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1. Baseline (single model)</t>
+          <t>1. Baseline (single model, superseded)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4287,14 +5238,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Own train_test_split; test set not comparable to canonical 984-row test set</t>
+          <t>Own train_test_split; test set not comparable to canonical 984-row test set. Superseded by stage 0. Note the four 'BERT + X' rows are BERT TOKENIZER + X - there is no BERT encoder in the baseline scripts.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1. Baseline (single model)</t>
+          <t>1. Baseline (single model, superseded)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4335,14 +5286,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Own train_test_split; test set not comparable to canonical 984-row test set</t>
+          <t>Own train_test_split; test set not comparable to canonical 984-row test set. Superseded by stage 0. Note the four 'BERT + X' rows are BERT TOKENIZER + X - there is no BERT encoder in the baseline scripts.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1. Baseline (single model)</t>
+          <t>1. Baseline (single model, superseded)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4383,14 +5334,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Own train_test_split; test set not comparable to canonical 984-row test set</t>
+          <t>Own train_test_split; test set not comparable to canonical 984-row test set. Superseded by stage 0. Note the four 'BERT + X' rows are BERT TOKENIZER + X - there is no BERT encoder in the baseline scripts.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1. Baseline (single model)</t>
+          <t>1. Baseline (single model, superseded)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4431,14 +5382,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Own train_test_split; test set not comparable to canonical 984-row test set</t>
+          <t>Own train_test_split; test set not comparable to canonical 984-row test set. Superseded by stage 0. Note the four 'BERT + X' rows are BERT TOKENIZER + X - there is no BERT encoder in the baseline scripts.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1. Baseline (single model)</t>
+          <t>1. Baseline (single model, superseded)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4479,7 +5430,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Own train_test_split; test set not comparable to canonical 984-row test set</t>
+          <t>Own train_test_split; test set not comparable to canonical 984-row test set. Superseded by stage 0. Note the four 'BERT + X' rows are BERT TOKENIZER + X - there is no BERT encoder in the baseline scripts.</t>
         </is>
       </c>
     </row>
